--- a/04_DESIGN_TABLES/DesignTable_2601_SW2.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_2601_SW2.xlsx
@@ -946,12 +946,17 @@
       </c>
       <c r="BK2" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="BL2" t="inlineStr">
         <is>
           <t>Air-Way s170 only (double-pass 29 rows; survey said 28 - page wins); JIC ends VERIFIED (MS33656J); MS51512 exists, untranscribed | MODEL: forged hex body per the 2603HX pattern (Brennan 2603 + 2650 STEPs): hex bars A/F = max(Air-Way hex, male thread majors), flats normal to Z, run bar continuous through the branch, branch hex arm; hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); each leg bore runs from its face to the axis crossing</t>
+        </is>
+      </c>
+      <c r="BM2" t="inlineStr">
+        <is>
+          <t>A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on M1@DRIVE=1.33~1.330; M2@DRIVE=1.33~1.330; N@DRIVE=1.47~1.470; Y@REF=0.88~0.875; D1@BORE=0.39~0.391; D2@BORE=0.39~0.391; DDRILL@BORE=0.53~0.531</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
@@ -1163,12 +1168,17 @@
       </c>
       <c r="BK3" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="BL3" t="inlineStr">
         <is>
           <t>Air-Way s170 only (double-pass 29 rows; survey said 28 - page wins); JIC ends VERIFIED (MS33656J); MS51512 exists, untranscribed | MODEL: forged hex body per the 2603HX pattern (Brennan 2603 + 2650 STEPs): hex bars A/F = max(Air-Way hex, male thread majors), flats normal to Z, run bar continuous through the branch, branch hex arm; hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); each leg bore runs from its face to the axis crossing</t>
+        </is>
+      </c>
+      <c r="BM3" t="inlineStr">
+        <is>
+          <t>A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on M1@DRIVE=0.89~0.890; M2@DRIVE=0.89~0.890; N@DRIVE=0.78~0.780; Y@REF=0.44~0.438; D1@BORE=0.17~0.172; D2@BORE=0.17~0.172; DDRILL@BORE=0.19~0.188</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
@@ -1380,7 +1390,7 @@
       </c>
       <c r="BK4" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="BL4" t="inlineStr">
@@ -1390,7 +1400,7 @@
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>M legs 1.05 exceed non-FG 0.95 (FG &gt; non-FG, unusual) - as-printed</t>
+          <t>M legs 1.05 exceed non-FG 0.95 (FG &gt; non-FG, unusual) - as-printed | A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on M1@DRIVE=1.05~1.050; M2@DRIVE=1.05~1.050; N@DRIVE=1.09~1.090; Y@REF=0.56~0.562; D1@BORE=0.17~0.172; D2@BORE=0.17~0.172; DDRILL@BORE=0.28~0.281</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
@@ -1602,7 +1612,7 @@
       </c>
       <c r="BK5" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="BL5" t="inlineStr">
@@ -1612,7 +1622,7 @@
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>hex A/F raised from Air-Way 0.56 to 0.5625 (JIC thread major; 2603HX rule)</t>
+          <t>A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on M1@DRIVE=1.06~1.060; M2@DRIVE=1.06~1.060; N@DRIVE=1.09~1.090; Y@REF=0.56~0.562; D1@BORE=0.3~0.297; D2@BORE=0.3~0.297; DDRILL@BORE=0.28~0.281 | hex A/F raised from Air-Way 0.56 to 0.5625 (JIC thread major; 2603HX rule)</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
@@ -1824,12 +1834,17 @@
       </c>
       <c r="BK6" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="BL6" t="inlineStr">
         <is>
           <t>Air-Way s170 only (double-pass 29 rows; survey said 28 - page wins); JIC ends VERIFIED (MS33656J); MS51512 exists, untranscribed | MODEL: forged hex body per the 2603HX pattern (Brennan 2603 + 2650 STEPs): hex bars A/F = max(Air-Way hex, male thread majors), flats normal to Z, run bar continuous through the branch, branch hex arm; hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); each leg bore runs from its face to the axis crossing</t>
+        </is>
+      </c>
+      <c r="BM6" t="inlineStr">
+        <is>
+          <t>A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on M1@DRIVE=1.14~1.140; M2@DRIVE=1.14~1.140; N@DRIVE=1.22~1.220; Y@REF=0.75~0.750; D1@BORE=0.3~0.297; D2@BORE=0.3~0.297; DDRILL@BORE=0.41~0.406</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
@@ -2041,12 +2056,17 @@
       </c>
       <c r="BK7" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="BL7" t="inlineStr">
         <is>
           <t>Air-Way s170 only (double-pass 29 rows; survey said 28 - page wins); JIC ends VERIFIED (MS33656J); MS51512 exists, untranscribed | MODEL: forged hex body per the 2603HX pattern (Brennan 2603 + 2650 STEPs): hex bars A/F = max(Air-Way hex, male thread majors), flats normal to Z, run bar continuous through the branch, branch hex arm; hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); each leg bore runs from its face to the axis crossing</t>
+        </is>
+      </c>
+      <c r="BM7" t="inlineStr">
+        <is>
+          <t>A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on M1@DRIVE=1.25~1.250; M2@DRIVE=1.25~1.250; N@DRIVE=1.22~1.220; Y@REF=0.75~0.750; D1@BORE=0.39~0.391; D2@BORE=0.39~0.391; DDRILL@BORE=0.41~0.406</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
@@ -2258,7 +2278,7 @@
       </c>
       <c r="BK8" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="BL8" t="inlineStr">
@@ -2268,7 +2288,7 @@
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>hex A/F raised from Air-Way 1.06 to 1.0625 (JIC thread major; 2603HX rule); leg 3: male NPTF thread dia at L2 1.0589 vs hex flats 1.0625 (round end flush with the flats by 0.0018; Brennan 5600-16-16-16-FG also has its round end proud of the flats, by 0.0012)</t>
+          <t>A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on M1@DRIVE=1.66~1.660; M2@DRIVE=1.66~1.660; N@DRIVE=1.59~1.590; Y@REF=1.06~1.062; D1@BORE=0.61~0.609; D2@BORE=0.61~0.609; DDRILL@BORE=0.72~0.719 | hex A/F raised from Air-Way 1.06 to 1.0625 (JIC thread major; 2603HX rule); leg 3: male NPTF thread dia at L2 1.0589 vs hex flats 1.0625 (round end flush with the flats by 0.0018; Brennan 5600-16-16-16-FG also has its round end proud of the flats, by 0.0012)</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
@@ -2480,7 +2500,7 @@
       </c>
       <c r="BK9" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="BL9" t="inlineStr">
@@ -2490,7 +2510,7 @@
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>hex A/F raised from Air-Way 1.31 to 1.3125 (JIC thread major; 2603HX rule); leg 3: male NPTF thread dia at L2 1.3259 vs hex flats 1.3125 (round end proud of the flats by 0.0067; Brennan 5600-16-16-16-FG also has its round end proud of the flats, by 0.0012)</t>
+          <t>A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on M1@DRIVE=1.81~1.810; M2@DRIVE=1.81~1.810; N@DRIVE=1.97~1.970; Y@REF=1.31~1.312; D1@BORE=0.84~0.844; D2@BORE=0.84~0.844; DDRILL@BORE=0.94~0.938 | hex A/F raised from Air-Way 1.31 to 1.3125 (JIC thread major; 2603HX rule); leg 3: male NPTF thread dia at L2 1.3259 vs hex flats 1.3125 (round end proud of the flats by 0.0067; Brennan 5600-16-16-16-FG also has its round end proud of the flats, by 0.0012)</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
@@ -2702,7 +2722,7 @@
       </c>
       <c r="BK10" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="BL10" t="inlineStr">
@@ -2712,7 +2732,7 @@
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>B(2) printed "1 5/4-12" both passes (typo for 1 5/8-12) - corrected thread used, as-printed in note | leg 3: male NPTF thread dia at L2 1.6709 vs hex flats 1.6300 (round end proud of the flats by 0.0204; Brennan 5600-16-16-16-FG also has its round end proud of the flats, by 0.0012)</t>
+          <t>B(2) printed "1 5/4-12" both passes (typo for 1 5/8-12) - corrected thread used, as-printed in note | A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on M1@DRIVE=2.06~2.060; M2@DRIVE=2.06~2.060; N@DRIVE=2.38~2.380; Y@REF=1.63~1.625; D1@BORE=1.08~1.078; D2@BORE=1.08~1.078; DDRILL@BORE=1.25~1.25 | leg 3: male NPTF thread dia at L2 1.6709 vs hex flats 1.6300 (round end proud of the flats by 0.0204; Brennan 5600-16-16-16-FG also has its round end proud of the flats, by 0.0012)</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
